--- a/artfynd/A 6031-2025 artfynd.xlsx
+++ b/artfynd/A 6031-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123727120</v>
+        <v>123727136</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>79868</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -761,6 +761,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Nils Ericson</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123727136</v>
+        <v>123727120</v>
       </c>
       <c r="B3" t="n">
-        <v>79863</v>
+        <v>79896</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -863,11 +868,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Nils Ericson</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 6031-2025 artfynd.xlsx
+++ b/artfynd/A 6031-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123727136</v>
+        <v>123727120</v>
       </c>
       <c r="B2" t="n">
-        <v>79868</v>
+        <v>79898</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -761,11 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Nils Ericson</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123727120</v>
+        <v>123727136</v>
       </c>
       <c r="B3" t="n">
-        <v>79896</v>
+        <v>79870</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -868,6 +863,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Nils Ericson</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
